--- a/reports/ibis_files/hark_cbg256_package_pin/hark_cbg256_package_pin.xlsx
+++ b/reports/ibis_files/hark_cbg256_package_pin/hark_cbg256_package_pin.xlsx
@@ -113,7 +113,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09T23:35:12-05:00</t>
+          <t>2026-06-12T22:46:17-05:00</t>
         </is>
       </c>
     </row>

--- a/reports/ibis_files/hark_cbg256_package_pin/hark_cbg256_package_pin.xlsx
+++ b/reports/ibis_files/hark_cbg256_package_pin/hark_cbg256_package_pin.xlsx
@@ -113,7 +113,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12T22:46:17-05:00</t>
+          <t>2026-06-13T23:04:05-05:00</t>
         </is>
       </c>
     </row>
